--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,1291 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126196634</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>484297</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6837946</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126196132</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6837758</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126196588</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6837952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126196217</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484328</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6837792</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126196449</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484379</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6837944</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126198143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>484186</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6837902</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126196300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>484418</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6837788</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126196884</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>484277</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6837955</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126196475</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97225</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>484383</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6837980</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126196428</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>484392</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6837928</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126196453</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>484381</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6837948</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126196128</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>484359</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6837754</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126196268</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98341</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korrissjön, Korrissjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>484344</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6837810</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Tät matta av knärot i kolbotten.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126196634</v>
+        <v>126196132</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -928,17 +928,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484297</v>
+        <v>484357</v>
       </c>
       <c r="R4" t="n">
-        <v>6837946</v>
+        <v>6837758</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126196132</v>
+        <v>126196634</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1025,17 +1025,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484357</v>
+        <v>484297</v>
       </c>
       <c r="R5" t="n">
-        <v>6837758</v>
+        <v>6837946</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
         <v>126196475</v>
       </c>
       <c r="B12" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,48 +1969,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126196128</v>
+        <v>126196268</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484359</v>
+        <v>484344</v>
       </c>
       <c r="R15" t="n">
-        <v>6837754</v>
+        <v>6837810</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,7 +2053,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Tät matta av knärot i kolbotten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2059,69 +2068,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126196268</v>
+        <v>126196128</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484344</v>
+        <v>484359</v>
       </c>
       <c r="R16" t="n">
-        <v>6837810</v>
+        <v>6837754</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tät matta av knärot i kolbotten.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,12 +2170,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126196132</v>
+        <v>126196634</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -928,17 +928,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484357</v>
+        <v>484297</v>
       </c>
       <c r="R4" t="n">
-        <v>6837758</v>
+        <v>6837946</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126196634</v>
+        <v>126196132</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1025,17 +1025,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484297</v>
+        <v>484357</v>
       </c>
       <c r="R5" t="n">
-        <v>6837946</v>
+        <v>6837758</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
         <v>126196475</v>
       </c>
       <c r="B12" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,57 +1969,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126196268</v>
+        <v>126196128</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484344</v>
+        <v>484359</v>
       </c>
       <c r="R15" t="n">
-        <v>6837810</v>
+        <v>6837754</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tät matta av knärot i kolbotten.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2068,60 +2059,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126196128</v>
+        <v>126196268</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484359</v>
+        <v>484344</v>
       </c>
       <c r="R16" t="n">
-        <v>6837754</v>
+        <v>6837810</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Tät matta av knärot i kolbotten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,12 +2170,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>126196634</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>126196132</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126196588</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>126196217</v>
       </c>
       <c r="B7" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>126196449</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126198143</v>
       </c>
       <c r="B9" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>126196300</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>126196884</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>126196475</v>
       </c>
       <c r="B12" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>126196428</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126196453</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>126196128</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>126196268</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126196634</v>
+        <v>126196132</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -928,17 +928,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484297</v>
+        <v>484357</v>
       </c>
       <c r="R4" t="n">
-        <v>6837946</v>
+        <v>6837758</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126196132</v>
+        <v>126196634</v>
       </c>
       <c r="B5" t="n">
         <v>78977</v>
@@ -1025,17 +1025,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484357</v>
+        <v>484297</v>
       </c>
       <c r="R5" t="n">
-        <v>6837758</v>
+        <v>6837946</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
         <v>126196475</v>
       </c>
       <c r="B12" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,48 +1969,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126196128</v>
+        <v>126196268</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484359</v>
+        <v>484344</v>
       </c>
       <c r="R15" t="n">
-        <v>6837754</v>
+        <v>6837810</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,7 +2053,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Tät matta av knärot i kolbotten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2059,69 +2068,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126196268</v>
+        <v>126196128</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484344</v>
+        <v>484359</v>
       </c>
       <c r="R16" t="n">
-        <v>6837810</v>
+        <v>6837754</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tät matta av knärot i kolbotten.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,12 +2170,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -1969,57 +1969,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126196268</v>
+        <v>126196128</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484344</v>
+        <v>484359</v>
       </c>
       <c r="R15" t="n">
-        <v>6837810</v>
+        <v>6837754</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tät matta av knärot i kolbotten.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2068,60 +2059,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126196128</v>
+        <v>126196268</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484359</v>
+        <v>484344</v>
       </c>
       <c r="R16" t="n">
-        <v>6837754</v>
+        <v>6837810</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Tät matta av knärot i kolbotten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,12 +2170,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126196132</v>
+        <v>126196634</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,17 +928,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484357</v>
+        <v>484297</v>
       </c>
       <c r="R4" t="n">
-        <v>6837758</v>
+        <v>6837946</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126196634</v>
+        <v>126196132</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,17 +1025,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484297</v>
+        <v>484357</v>
       </c>
       <c r="R5" t="n">
-        <v>6837946</v>
+        <v>6837758</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
         <v>126196588</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>126196217</v>
       </c>
       <c r="B7" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>126196449</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126198143</v>
       </c>
       <c r="B9" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>126196300</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>126196884</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>126196475</v>
       </c>
       <c r="B12" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>126196428</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126196453</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>126196128</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>126196268</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126196634</v>
+        <v>126196132</v>
       </c>
       <c r="B4" t="n">
         <v>78980</v>
@@ -928,17 +928,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484297</v>
+        <v>484357</v>
       </c>
       <c r="R4" t="n">
-        <v>6837946</v>
+        <v>6837758</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126196132</v>
+        <v>126196634</v>
       </c>
       <c r="B5" t="n">
         <v>78980</v>
@@ -1025,17 +1025,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484357</v>
+        <v>484297</v>
       </c>
       <c r="R5" t="n">
-        <v>6837758</v>
+        <v>6837946</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -1969,48 +1969,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126196128</v>
+        <v>126196268</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484359</v>
+        <v>484344</v>
       </c>
       <c r="R15" t="n">
-        <v>6837754</v>
+        <v>6837810</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,7 +2053,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Tät matta av knärot i kolbotten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2059,69 +2068,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126196268</v>
+        <v>126196128</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484344</v>
+        <v>484359</v>
       </c>
       <c r="R16" t="n">
-        <v>6837810</v>
+        <v>6837754</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tät matta av knärot i kolbotten.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,12 +2170,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 51222-2023 artfynd.xlsx
+++ b/artfynd/A 51222-2023 artfynd.xlsx
@@ -1969,57 +1969,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126196268</v>
+        <v>126196128</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korrissjön, Korrissjön, Dlr</t>
+          <t>Gethelvetet, Gethelvetet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484344</v>
+        <v>484359</v>
       </c>
       <c r="R15" t="n">
-        <v>6837810</v>
+        <v>6837754</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,7 +2044,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Tät matta av knärot i kolbotten.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2068,60 +2059,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126196128</v>
+        <v>126196268</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gethelvetet, Gethelvetet, Dlr</t>
+          <t>Korrissjön, Korrissjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484359</v>
+        <v>484344</v>
       </c>
       <c r="R16" t="n">
-        <v>6837754</v>
+        <v>6837810</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Tät matta av knärot i kolbotten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,12 +2170,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
